--- a/data/trans_orig/P20B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29452</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>37537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>71303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>77766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89840</t>
+          <t>90270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>31207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28418</t>
+          <t>28799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>21083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23901</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>30448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42927</t>
+          <t>43187</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>37830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48477</t>
+          <t>48496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>71546</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102057</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88294</t>
+          <t>88128</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108708</t>
+          <t>107860</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>185435</t>
+          <t>186288</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>209426</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280292</t>
+          <t>279911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>312398</t>
+          <t>310803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26850</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45932</t>
+          <t>45746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>27714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73949</t>
+          <t>74360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83280</t>
+          <t>83339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97231</t>
+          <t>97545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109223</t>
+          <t>109281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19881</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20739</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39199</t>
+          <t>40560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30423</t>
+          <t>30360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44629</t>
+          <t>45485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53901</t>
+          <t>52540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72361</t>
+          <t>71952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30846</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>24744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>32510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34985</t>
+          <t>35266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52992</t>
+          <t>53569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43223</t>
+          <t>43432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28640</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24422</t>
+          <t>24067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26661</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22983</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31842</t>
+          <t>31082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41965</t>
+          <t>41176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59067</t>
+          <t>58077</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>73003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48081</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78523</t>
+          <t>78396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66734</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98443</t>
+          <t>98841</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125411</t>
+          <t>122540</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>167472</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>129369</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>159684</t>
+          <t>158459</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>236093</t>
+          <t>235695</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>268412</t>
+          <t>267802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>376259</t>
+          <t>374829</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>416890</t>
+          <t>419761</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016 (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24920</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>43235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50394</t>
+          <t>50893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58879</t>
+          <t>58821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61640</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71236</t>
+          <t>71180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46677</t>
+          <t>45026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61019</t>
+          <t>61087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32338</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21639</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>37112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17714</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35151</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18376</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22874</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>36765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>30378</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>32283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35835</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51074</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37289</t>
+          <t>37856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>50800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>81415</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101246</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96117</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119975</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>189684</t>
+          <t>188116</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>217828</t>
+          <t>218731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>291088</t>
+          <t>289558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>330762</t>
+          <t>329585</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12777</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>57,78%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13233</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>59,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>12394</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>36338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49851</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>31414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37829</t>
+          <t>36847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49810</t>
+          <t>48862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>34570</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32223</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47106</t>
+          <t>47385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33136</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>22827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35797</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42541</t>
+          <t>41918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56938</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>25210</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>27595</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34744</t>
+          <t>34463</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60011</t>
+          <t>60117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74594</t>
+          <t>74818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>61718</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95101</t>
+          <t>96172</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129204</t>
+          <t>129947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113464</t>
+          <t>113240</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138419</t>
+          <t>137617</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>156316</t>
+          <t>155125</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>177176</t>
+          <t>176751</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>274955</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>309801</t>
+          <t>308730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22088</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>37501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61583</t>
+          <t>61503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>71161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77766</t>
+          <t>77494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90270</t>
+          <t>90435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>32514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43675</t>
+          <t>44098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28799</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21083</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30448</t>
+          <t>29828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>42597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37830</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>48425</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>63528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71546</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102438</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88128</t>
+          <t>88556</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>184839</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>211612</t>
+          <t>209743</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279911</t>
+          <t>279846</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>311987</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34339</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45746</t>
+          <t>45893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>27666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74360</t>
+          <t>74339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83339</t>
+          <t>83273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97545</t>
+          <t>96279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109281</t>
+          <t>109224</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24768</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40560</t>
+          <t>40480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>30444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52540</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71952</t>
+          <t>71897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48572</t>
+          <t>48855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,27%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13252</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35266</t>
+          <t>34983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53569</t>
+          <t>53768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22587</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>28303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>42498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24067</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>33966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22359</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34099</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>41090</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>59087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73003</t>
+          <t>73756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78396</t>
+          <t>77457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>67275</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98841</t>
+          <t>99595</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>167472</t>
+          <t>166310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>130308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>158459</t>
+          <t>159105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>235695</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>267802</t>
+          <t>267261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>374829</t>
+          <t>375991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>419761</t>
+          <t>416369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -6691,62 +6691,62 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6480</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2434</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6527</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2434</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7536</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,49 +6819,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>30527</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24924</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>32961</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30527</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25425</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32961</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>77,14%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>39</t>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43235</t>
+          <t>43249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58821</t>
+          <t>58835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61517</t>
+          <t>61690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71180</t>
+          <t>71229</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27499</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34828</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>46251</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45026</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>61572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>19919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23053</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37112</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21270</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>22859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36765</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30378</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35492</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>51176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>19516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19535</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>21049</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>34826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37856</t>
+          <t>37411</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52171</t>
+          <t>52590</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50800</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102423</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>140282</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95274</t>
+          <t>93986</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>119183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188116</t>
+          <t>187960</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>218731</t>
+          <t>216722</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289558</t>
+          <t>291726</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>329585</t>
+          <t>330203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>14524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>34695</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27210</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>44805</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>42824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49712</t>
+          <t>57361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,67 +10386,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>33,63%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>14745</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>8897</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>21961</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>22,74%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13119</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>20263</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>21591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,67 +10499,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27631</t>
+          <t>32135</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>36052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>78,5%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>66,37%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>50093</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>42877</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>55941</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>77,26%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>63,86%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>87,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>43991</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>36847</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>48862</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>77,03%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>24137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>23001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34570</t>
+          <t>40274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>24827</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>42895</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32078</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47385</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12673</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>38286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>26730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49970</t>
+          <t>54544</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41918</t>
+          <t>46890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56736</t>
+          <t>61502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75677</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75677</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75677</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>20474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>20136</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>36652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>48281</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>37849</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>37849</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>37849</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>55670</t>
+          <t>58862</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>52251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60117</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>71808</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71808</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71808</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50441</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74818</t>
+          <t>81090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61718</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96172</t>
+          <t>108858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129947</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>125782</t>
+          <t>136976</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113240</t>
+          <t>124088</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137617</t>
+          <t>150311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>167000</t>
+          <t>188182</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155125</t>
+          <t>173814</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>176751</t>
+          <t>200136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>292782</t>
+          <t>325158</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>274955</t>
+          <t>306091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>308730</t>
+          <t>341787</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
